--- a/innolight/dist/20261026_中際旭創模型_v0.2.2.xlsx
+++ b/innolight/dist/20261026_中際旭創模型_v0.2.2.xlsx
@@ -6468,26 +6468,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6705,26 +6705,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6826,26 +6826,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6947,26 +6947,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7068,26 +7068,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7189,26 +7189,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -34381,7 +34381,7 @@
         <v>33</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>34</v>
